--- a/Bases de datos/clean/dic_arg_proy_2005_2018.xlsx
+++ b/Bases de datos/clean/dic_arg_proy_2005_2018.xlsx
@@ -1,128 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Procesamiento-R\Bases de datos\clean\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19301295-19B6-4CBF-AB2A-D4705C8BA859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
-  <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>tipo_var</t>
-  </si>
-  <si>
-    <t>valores</t>
-  </si>
-  <si>
-    <t>anio_enfr</t>
-  </si>
-  <si>
-    <t>Año de realización ENFR</t>
-  </si>
-  <si>
-    <t>factor</t>
-  </si>
-  <si>
-    <t>2005, 2009, 2013, 2018</t>
-  </si>
-  <si>
-    <t>anio</t>
-  </si>
-  <si>
-    <t>Año para la proyección poblacional (para 2009 se interpoló linealmente a partir de 2005 y 2010)</t>
-  </si>
-  <si>
-    <t>2005, 2010, 2013, 2018</t>
-  </si>
-  <si>
-    <t>prov_id</t>
-  </si>
-  <si>
-    <t>Identificador numérico de provincia</t>
-  </si>
-  <si>
-    <t>2, 6, 10, 14, 18, 22, 26, 30, 34, 38, 42, 46, 50, 54, 58, 62, 66, 70, 74, 78, 82, 86, 90, 94</t>
-  </si>
-  <si>
-    <t>prov_nombre</t>
-  </si>
-  <si>
-    <t>Identificador categórico de provincia</t>
-  </si>
-  <si>
-    <t>Buenos Aires, CABA, Catamarca, Chaco, Chubut, Córdoba, Corrientes, Entre Ríos, Formosa, Jujuy, La Pampa, La Rioja, Mendoza, Misiones, Neuquén, Río Negro, Salta, San Juan, San Luis, Santa Cruz, Santa Fe, Santiago del Estero, Tierra del Fuego, Tucumán</t>
-  </si>
-  <si>
-    <t>grupo_edad_5</t>
-  </si>
-  <si>
-    <t>Grupo de edad quinquenal</t>
-  </si>
-  <si>
-    <t>20-24 años, 25-29 años, 30-34 años, 35-39 años, 40-44 años, 45-49 años, 50-54 años, 55-59 años, 60-64 años, 65-69 años, 70-74 años, 75-79 años, 80+ años</t>
-  </si>
-  <si>
-    <t>grupo_edad_10</t>
-  </si>
-  <si>
-    <t>Grupo de edad decenal</t>
-  </si>
-  <si>
-    <t>20-29 años, 30-39 años, 40-49 años, 50-59 años, 60-69 años, 70-79 años, 80+ años</t>
-  </si>
-  <si>
-    <t>sexo</t>
-  </si>
-  <si>
-    <t>Sexo biológico</t>
-  </si>
-  <si>
-    <t>Varón, Mujer</t>
-  </si>
-  <si>
-    <t>proy_pob</t>
-  </si>
-  <si>
-    <t>Proyección poblacional</t>
-  </si>
-  <si>
-    <t>numeric</t>
-  </si>
-  <si>
-    <t>0-Inf</t>
-  </si>
-  <si>
-    <t>pob_est_2010</t>
-  </si>
-  <si>
-    <t>Población estándar Censo 2010</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,16 +52,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -176,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -262,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -297,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,154 +350,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="229" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>29</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_var</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>valores</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>anio_enfr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Año de realización ENFR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2005, 2009, 2013, 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>anio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Año para la proyección poblacional (para 2009 se interpoló linealmente a partir de 2005 y 2010)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2005, 2010, 2013, 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>prov_id</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Identificador numérico de provincia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2, 6, 10, 14, 18, 22, 26, 30, 34, 38, 42, 46, 50, 54, 58, 62, 66, 70, 74, 78, 82, 86, 90, 94</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>prov_nombre</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Identificador categórico de provincia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Buenos Aires, CABA, Catamarca, Chaco, Chubut, Córdoba, Corrientes, Entre Ríos, Formosa, Jujuy, La Pampa, La Rioja, Mendoza, Misiones, Neuquén, Río Negro, Salta, San Juan, San Luis, Santa Cruz, Santa Fe, Santiago del Estero, Tierra del Fuego, Tucumán</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>grupo_edad_5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Grupo de edad quinquenal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20-24 años, 25-29 años, 30-34 años, 35-39 años, 40-44 años, 45-49 años, 50-54 años, 55-59 años, 60-64 años, 65-69 años, 70-74 años, 75-79 años, 80+ años</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>grupo_edad_10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grupo de edad decenal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20-29 años, 30-39 años, 40-49 años, 50-59 años, 60-69 años, 70-79 años, 80+ años</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sexo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sexo biológico</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Varón, Mujer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>proy_pob</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Proyección poblacional</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pob_est_2010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Población estándar Censo 2010</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0-Inf</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Bases de datos/clean/dic_arg_proy_2005_2018.xlsx
+++ b/Bases de datos/clean/dic_arg_proy_2005_2018.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -460,19 +460,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Buenos Aires, CABA, Catamarca, Chaco, Chubut, Córdoba, Corrientes, Entre Ríos, Formosa, Jujuy, La Pampa, La Rioja, Mendoza, Misiones, Neuquén, Río Negro, Salta, San Juan, San Luis, Santa Cruz, Santa Fe, Santiago del Estero, Tierra del Fuego, Tucumán</t>
+          <t>NULL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>grupo_edad_5</t>
+          <t>grupo_edad_10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grupo de edad quinquenal</t>
+          <t>Grupo de edad decenal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -482,19 +482,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20-24 años, 25-29 años, 30-34 años, 35-39 años, 40-44 años, 45-49 años, 50-54 años, 55-59 años, 60-64 años, 65-69 años, 70-74 años, 75-79 años, 80+ años</t>
+          <t>20-29, 30-39, 40-49, 50-59, 60-69, 70-79, 80+</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>grupo_edad_10</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grupo de edad decenal</t>
+          <t>Sexo biológico</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -504,41 +504,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20-29 años, 30-39 años, 40-49 años, 50-59 años, 60-69 años, 70-79 años, 80+ años</t>
+          <t>Varón, Mujer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>proy_pob</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sexo biológico</t>
+          <t>Proyección poblacional</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>factor</t>
+          <t>numeric</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Varón, Mujer</t>
+          <t>0-Inf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>proy_pob</t>
+          <t>pob_est_2010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Proyección poblacional</t>
+          <t>Población estándar Censo 2010</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -547,28 +547,6 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>0-Inf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pob_est_2010</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Población estándar Censo 2010</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>numeric</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>0-Inf</t>
         </is>
